--- a/artfynd/A 37068-2025 artfynd.xlsx
+++ b/artfynd/A 37068-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>127638711</v>
       </c>
       <c r="B3" t="n">
-        <v>100629</v>
+        <v>100630</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37068-2025 artfynd.xlsx
+++ b/artfynd/A 37068-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127638106</v>
       </c>
       <c r="B2" t="n">
-        <v>95768</v>
+        <v>95770</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127638711</v>
       </c>
       <c r="B3" t="n">
-        <v>100630</v>
+        <v>100632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37068-2025 artfynd.xlsx
+++ b/artfynd/A 37068-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127638106</v>
       </c>
       <c r="B2" t="n">
-        <v>95770</v>
+        <v>95776</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127638711</v>
       </c>
       <c r="B3" t="n">
-        <v>100632</v>
+        <v>100638</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37068-2025 artfynd.xlsx
+++ b/artfynd/A 37068-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127638106</v>
       </c>
       <c r="B2" t="n">
-        <v>95776</v>
+        <v>95779</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127638711</v>
       </c>
       <c r="B3" t="n">
-        <v>100638</v>
+        <v>100641</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37068-2025 artfynd.xlsx
+++ b/artfynd/A 37068-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127638106</v>
       </c>
       <c r="B2" t="n">
-        <v>95779</v>
+        <v>95787</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127638711</v>
       </c>
       <c r="B3" t="n">
-        <v>100641</v>
+        <v>100649</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37068-2025 artfynd.xlsx
+++ b/artfynd/A 37068-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127638106</v>
       </c>
       <c r="B2" t="n">
-        <v>95787</v>
+        <v>95788</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127638711</v>
       </c>
       <c r="B3" t="n">
-        <v>100649</v>
+        <v>100650</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37068-2025 artfynd.xlsx
+++ b/artfynd/A 37068-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127638106</v>
       </c>
       <c r="B2" t="n">
-        <v>95788</v>
+        <v>95789</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127638711</v>
       </c>
       <c r="B3" t="n">
-        <v>100650</v>
+        <v>100651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37068-2025 artfynd.xlsx
+++ b/artfynd/A 37068-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127638106</v>
       </c>
       <c r="B2" t="n">
-        <v>95789</v>
+        <v>95790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127638711</v>
       </c>
       <c r="B3" t="n">
-        <v>100651</v>
+        <v>100652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37068-2025 artfynd.xlsx
+++ b/artfynd/A 37068-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127638106</v>
+        <v>127637947</v>
       </c>
       <c r="B2" t="n">
-        <v>95790</v>
+        <v>96437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532832</v>
+        <v>532850</v>
       </c>
       <c r="R2" t="n">
-        <v>6437411</v>
+        <v>6437419</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127638711</v>
+        <v>127638106</v>
       </c>
       <c r="B3" t="n">
-        <v>100652</v>
+        <v>96426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532823</v>
+        <v>532832</v>
       </c>
       <c r="R3" t="n">
-        <v>6437415</v>
+        <v>6437411</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,15 +877,453 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Carina Faxén</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Carina Faxén</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127639064</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lidkullarna, Lidkullarna, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>532840</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6437425</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Västra Eneby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Carina Faxén</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Carina Faxén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127639312</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lidkullarna, Lidkullarna, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>532834</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6437452</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Västra Eneby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gammalt boträd. Kan även hysa andra arter.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Johan Holmgren</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Johan Holmgren</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127639058</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lidkullarna, Lidkullarna, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>532834</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6437452</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Västra Eneby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flera gnagspår på levande tall.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127638711</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lidkullarna, Lidkullarna, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>532823</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6437415</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Västra Eneby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37068-2025 artfynd.xlsx
+++ b/artfynd/A 37068-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127637947</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127638106</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127639064</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127639312</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127639058</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,8 +1354,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127638711</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>